--- a/AutomatizadorDePlanilha/planilha/planilha_lote_08abr_13abr.xlsx
+++ b/AutomatizadorDePlanilha/planilha/planilha_lote_08abr_13abr.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD92"/>
+  <dimension ref="A1:BD93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25634,7 +25634,6 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>2026_04_13_9</t>
@@ -25901,6 +25900,284 @@
         </is>
       </c>
       <c r="BD92" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026_04_08_3</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SECRETARIA DA SAUDE</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Dispensa de Licitação</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>menor preço</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>191380068 - MANUTENÇÃO DE ENGENHARIA CLINICA</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>COMPLEXO HOSPITALAR DE VITORIA DA CONQUISTA</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>🚨 SERVIÇO/RISCO DETECTADO - Instalação física</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>RADIO TRANSCEPTOR</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>10,00 UNIDADE</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="BD93" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
